--- a/output/Chp3_tables/Chp3 - Table3.xlsx
+++ b/output/Chp3_tables/Chp3 - Table3.xlsx
@@ -51,175 +51,175 @@
     <t>Expansion scenario</t>
   </si>
   <si>
-    <t>47.2 (22.6 - 115.6)</t>
-  </si>
-  <si>
-    <t>52.4 (27.0 - 122.2)</t>
-  </si>
-  <si>
-    <t>55.9 (29.9 - 127.4)</t>
-  </si>
-  <si>
-    <t>58.7 (32.2 - 130.3)</t>
-  </si>
-  <si>
-    <t>76.4 (43.3 - 179.5)</t>
+    <t>47.7 (23.4 - 106.8)</t>
+  </si>
+  <si>
+    <t>52.9 (27.7 - 112.9)</t>
+  </si>
+  <si>
+    <t>57.2 (31.7 - 116.2)</t>
+  </si>
+  <si>
+    <t>60.6 (34.0 - 118.9)</t>
+  </si>
+  <si>
+    <t>80.4 (45.5 - 163.6)</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>5.2 (1.8 - 11.7)</t>
-  </si>
-  <si>
-    <t>3.5 (1.2 - 7.6)</t>
-  </si>
-  <si>
-    <t>2.8 (0.9 - 6.2)</t>
-  </si>
-  <si>
-    <t>17.7 (8.3 - 60.8)</t>
-  </si>
-  <si>
-    <t>27,959 (15,141 - 47,770)</t>
-  </si>
-  <si>
-    <t>27,938 (15,092 - 47,740)</t>
-  </si>
-  <si>
-    <t>27,925 (15,081 - 47,720)</t>
-  </si>
-  <si>
-    <t>27,916 (15,072 - 47,707)</t>
-  </si>
-  <si>
-    <t>27,903 (15,067 - 47,696)</t>
-  </si>
-  <si>
-    <t>21,211 (3,815 - 80,829)</t>
-  </si>
-  <si>
-    <t>12,936 (1,846 - 51,001)</t>
-  </si>
-  <si>
-    <t>8,851 (1,042 - 34,506)</t>
-  </si>
-  <si>
-    <t>13,784 (208 - 31,184)</t>
-  </si>
-  <si>
-    <t>244 (21 - 983)</t>
-  </si>
-  <si>
-    <t>272 (14 - 1,302)</t>
-  </si>
-  <si>
-    <t>319 (19 - 1,991)</t>
-  </si>
-  <si>
-    <t>1,283 (759 - 42,733)</t>
-  </si>
-  <si>
-    <t>20.7 (11.1 - 37.4)</t>
-  </si>
-  <si>
-    <t>25.8 (15.2 - 42.7)</t>
-  </si>
-  <si>
-    <t>30.8 (19.5 - 48.9)</t>
-  </si>
-  <si>
-    <t>5.0 (2.7 - 8.3)</t>
-  </si>
-  <si>
-    <t>5.1 (3.0 - 9.5)</t>
-  </si>
-  <si>
-    <t>22,243 (12,192 - 37,232)</t>
-  </si>
-  <si>
-    <t>22,236 (12,175 - 37,224)</t>
-  </si>
-  <si>
-    <t>22,236 (12,174 - 37,224)</t>
-  </si>
-  <si>
-    <t>7,167 (2,485 - 14,531)</t>
-  </si>
-  <si>
-    <t>108 (-15 - 1,058)</t>
-  </si>
-  <si>
-    <t>704 (319 - 1,909)</t>
-  </si>
-  <si>
-    <t>47,044 (-125,588 - 190,672)</t>
-  </si>
-  <si>
-    <t>26.6 (14.2 - 48.9)</t>
-  </si>
-  <si>
-    <t>29.5 (16.7 - 52.8)</t>
-  </si>
-  <si>
-    <t>31.7 (18.4 - 55.3)</t>
-  </si>
-  <si>
-    <t>33.7 (19.8 - 57.4)</t>
-  </si>
-  <si>
-    <t>42.3 (26.6 - 68.9)</t>
-  </si>
-  <si>
-    <t>2.9 (1.6 - 5.3)</t>
-  </si>
-  <si>
-    <t>2.3 (1.2 - 3.8)</t>
-  </si>
-  <si>
-    <t>2.0 (1.0 - 3.1)</t>
-  </si>
-  <si>
-    <t>8.5 (4.8 - 17.6)</t>
-  </si>
-  <si>
-    <t>23,902 (13,083 - 40,305)</t>
-  </si>
-  <si>
-    <t>23,898 (13,074 - 40,298)</t>
-  </si>
-  <si>
-    <t>23,895 (13,067 - 40,293)</t>
-  </si>
-  <si>
-    <t>23,893 (13,062 - 40,289)</t>
-  </si>
-  <si>
-    <t>23,893 (13,061 - 40,288)</t>
-  </si>
-  <si>
-    <t>4,148 (2,107 - 15,842)</t>
-  </si>
-  <si>
-    <t>2,681 (1,393 - 10,774)</t>
-  </si>
-  <si>
-    <t>1,845 (966 - 7,661)</t>
-  </si>
-  <si>
-    <t>528 (46 - 4,091)</t>
-  </si>
-  <si>
-    <t>696 (171 - 1,346)</t>
-  </si>
-  <si>
-    <t>849 (186 - 1,547)</t>
-  </si>
-  <si>
-    <t>1,079 (212 - 1,888)</t>
-  </si>
-  <si>
-    <t>16,156 (2,498 - 79,731)</t>
+    <t>5.2 (2.7 - 10.1)</t>
+  </si>
+  <si>
+    <t>4.3 (2.0 - 7.1)</t>
+  </si>
+  <si>
+    <t>3.4 (1.7 - 6.3)</t>
+  </si>
+  <si>
+    <t>19.8 (9.6 - 46.7)</t>
+  </si>
+  <si>
+    <t>28,664 (17,125 - 46,487)</t>
+  </si>
+  <si>
+    <t>28,635 (17,046 - 46,469)</t>
+  </si>
+  <si>
+    <t>28,618 (17,005 - 46,460)</t>
+  </si>
+  <si>
+    <t>28,614 (16,980 - 46,454)</t>
+  </si>
+  <si>
+    <t>28,612 (16,968 - 46,449)</t>
+  </si>
+  <si>
+    <t>29,000 (6,061 - 69,013)</t>
+  </si>
+  <si>
+    <t>16,987 (3,628 - 43,971)</t>
+  </si>
+  <si>
+    <t>4,709 (2,329 - 29,600)</t>
+  </si>
+  <si>
+    <t>1,572 (310 - 21,883)</t>
+  </si>
+  <si>
+    <t>179 (73 - 818)</t>
+  </si>
+  <si>
+    <t>250 (81 - 1,145)</t>
+  </si>
+  <si>
+    <t>725 (98 - 1,649)</t>
+  </si>
+  <si>
+    <t>12,568 (1,026 - 35,633)</t>
+  </si>
+  <si>
+    <t>21.3 (11.3 - 37.6)</t>
+  </si>
+  <si>
+    <t>26.2 (15.7 - 43.3)</t>
+  </si>
+  <si>
+    <t>31.3 (19.7 - 49.1)</t>
+  </si>
+  <si>
+    <t>4.9 (3.0 - 8.1)</t>
+  </si>
+  <si>
+    <t>5.1 (3.1 - 7.8)</t>
+  </si>
+  <si>
+    <t>22,851 (13,639 - 36,263)</t>
+  </si>
+  <si>
+    <t>22,846 (13,629 - 36,255)</t>
+  </si>
+  <si>
+    <t>22,846 (13,628 - 36,255)</t>
+  </si>
+  <si>
+    <t>5,541 (3,300 - 13,831)</t>
+  </si>
+  <si>
+    <t>196 (-26 - 792)</t>
+  </si>
+  <si>
+    <t>892 (304 - 1,610)</t>
+  </si>
+  <si>
+    <t>25,952 (-123,467 - 271,316)</t>
+  </si>
+  <si>
+    <t>27.3 (14.4 - 49.4)</t>
+  </si>
+  <si>
+    <t>30.4 (17.0 - 53.0)</t>
+  </si>
+  <si>
+    <t>32.7 (19.0 - 55.6)</t>
+  </si>
+  <si>
+    <t>34.6 (20.6 - 57.8)</t>
+  </si>
+  <si>
+    <t>43.0 (27.5 - 67.8)</t>
+  </si>
+  <si>
+    <t>3.0 (1.7 - 5.1)</t>
+  </si>
+  <si>
+    <t>2.3 (1.3 - 3.7)</t>
+  </si>
+  <si>
+    <t>1.9 (1.1 - 3.1)</t>
+  </si>
+  <si>
+    <t>8.4 (5.1 - 14.7)</t>
+  </si>
+  <si>
+    <t>24,559 (14,621 - 39,239)</t>
+  </si>
+  <si>
+    <t>24,549 (14,609 - 39,232)</t>
+  </si>
+  <si>
+    <t>24,545 (14,601 - 39,228)</t>
+  </si>
+  <si>
+    <t>24,541 (14,596 - 39,225)</t>
+  </si>
+  <si>
+    <t>24,541 (14,595 - 39,224)</t>
+  </si>
+  <si>
+    <t>9,804 (2,870 - 14,464)</t>
+  </si>
+  <si>
+    <t>3,748 (1,979 - 9,805)</t>
+  </si>
+  <si>
+    <t>3,771 (1,402 - 7,211)</t>
+  </si>
+  <si>
+    <t>702 (10 - 2,873)</t>
+  </si>
+  <si>
+    <t>311 (178 - 1,109)</t>
+  </si>
+  <si>
+    <t>619 (200 - 1,238)</t>
+  </si>
+  <si>
+    <t>496 (227 - 1,530)</t>
+  </si>
+  <si>
+    <t>12,010 (2,150 - 90,129)</t>
   </si>
 </sst>
 </file>
